--- a/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>VTOL</t>
   </si>
@@ -656,173 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1297400</v>
+      </c>
+      <c r="E8" s="3">
         <v>922600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1185200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1178100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>226100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>221700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>231300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>247200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>281800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>331200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>299000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>990400</v>
+      </c>
+      <c r="E9" s="3">
         <v>714900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>918400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>890000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>154500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>167400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>169900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>171500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>204400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>186600</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E10" s="3">
         <v>207700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>266800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>288100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>70200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>63900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>110400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>126800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>112300</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,81 +924,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>6300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>187700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-41200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>117000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E15" s="3">
         <v>49600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>75000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>70100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>39500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>47300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>46300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45600</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,80 +1019,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1236800</v>
+      </c>
+      <c r="E17" s="3">
         <v>892800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1186800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1308700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>229400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>193400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>367800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>250100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>255900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>291000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>252800</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E18" s="3">
         <v>29800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-130700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>28200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-136500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46200</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,188 +1114,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>125300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E21" s="3">
         <v>111600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>124300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>85100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>36700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>68900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-90200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>84800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>83700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>92800</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E22" s="3">
         <v>30700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>51300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18100</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E23" s="3">
         <v>21100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-56600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-152700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29100</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E24" s="3">
         <v>7500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-52700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11700</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,81 +1345,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E26" s="3">
         <v>13600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-56300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17400</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>13500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-98200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1426,11 +1486,11 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3">
         <v>70000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,81 +1579,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-125300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>13500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18000</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,86 +1696,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>13500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18000</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,44 +1816,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180300</v>
+      </c>
+      <c r="E41" s="3">
         <v>160000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>263800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>228000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>50800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31300</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1802,242 +1891,263 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>234600</v>
+      </c>
+      <c r="E43" s="3">
         <v>215100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>203800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>215600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>61300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>35500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42500</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E44" s="3">
         <v>81900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>81700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>92200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>20100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>28000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>26900</v>
       </c>
       <c r="M44" s="3">
         <v>26900</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E45" s="3">
         <v>36100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4500</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>563600</v>
+      </c>
+      <c r="E46" s="3">
         <v>493100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>579900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>585700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>195900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>115900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>82600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>102500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>107800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105200</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E47" s="3">
         <v>17000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37500</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>27100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>35000</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1215700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1156200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1136100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1251200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>566400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>599200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>673900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>821800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2035100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>863100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>803700</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E49" s="3">
         <v>65800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>83900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1100</v>
       </c>
       <c r="I49" s="3">
         <v>1100</v>
@@ -2046,17 +2156,20 @@
         <v>1100</v>
       </c>
       <c r="K49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L49" s="3">
         <v>1200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>400</v>
       </c>
       <c r="M49" s="3">
         <v>400</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>400</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,45 +2242,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E52" s="3">
         <v>79800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14400</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,45 +2320,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1937300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1812000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1824300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1992300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>764500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>764900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>792100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>955200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1004400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1017200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>958600</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,224 +2396,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E57" s="3">
         <v>89600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>63500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13300</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E58" s="3">
         <v>11700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2800</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E59" s="3">
         <v>184300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>211500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>219600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14100</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>309800</v>
+      </c>
+      <c r="E60" s="3">
         <v>285600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>287800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>305100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30100</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>534800</v>
+      </c>
+      <c r="E61" s="3">
         <v>499800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>512900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>527500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>141800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>160200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>202200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>230100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>263700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>282100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>279400</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>269500</v>
+      </c>
+      <c r="E62" s="3">
         <v>239700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>188200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>261000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>112400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>109100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>226800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>232500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>219100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>213000</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,45 +2744,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1113600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1024700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>988500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1094700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>307800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>301400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>346400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>486800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>533000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>556500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>522300</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,45 +2956,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E72" s="3">
         <v>224700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>211200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>227000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14700</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,45 +3112,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>823700</v>
+      </c>
+      <c r="E76" s="3">
         <v>787300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>835800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>897600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>456700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>463400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>445700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>468400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>471300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>460700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>436300</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,86 +3190,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>13500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18000</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,44 +3293,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E83" s="3">
         <v>59800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>87200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>90500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>47300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45600</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,45 +3524,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>123900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>96800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>54400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>20100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>58500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>78300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>64400</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,44 +3583,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-106700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-110100</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,45 +3697,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>173300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>48600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>22800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-93900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43500</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3557,11 +3790,14 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-5000</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,115 +3909,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-63500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-245600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-33000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-46000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>26100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-102300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19800</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>VTOL</t>
   </si>
@@ -663,8 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -695,13 +695,13 @@
         <v>44286</v>
       </c>
       <c r="H7" s="2">
-        <v>43830</v>
+        <v>43921</v>
       </c>
       <c r="I7" s="2">
-        <v>43465</v>
+        <v>43555</v>
       </c>
       <c r="J7" s="2">
-        <v>43100</v>
+        <v>43190</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -722,25 +722,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1297400</v>
+        <v>1264300</v>
       </c>
       <c r="E8" s="3">
-        <v>922600</v>
+        <v>1173500</v>
       </c>
       <c r="F8" s="3">
-        <v>1185200</v>
+        <v>1139100</v>
       </c>
       <c r="G8" s="3">
-        <v>1178100</v>
+        <v>1139000</v>
       </c>
       <c r="H8" s="3">
-        <v>226100</v>
+        <v>1190600</v>
       </c>
       <c r="I8" s="3">
-        <v>221700</v>
+        <v>1307900</v>
       </c>
       <c r="J8" s="3">
-        <v>231300</v>
+        <v>1373400</v>
       </c>
       <c r="K8" s="3">
         <v>247200</v>
@@ -761,25 +761,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>990400</v>
+        <v>957600</v>
       </c>
       <c r="E9" s="3">
-        <v>714900</v>
+        <v>908400</v>
       </c>
       <c r="F9" s="3">
-        <v>918400</v>
+        <v>872900</v>
       </c>
       <c r="G9" s="3">
-        <v>890000</v>
+        <v>851200</v>
       </c>
       <c r="H9" s="3">
-        <v>154500</v>
+        <v>940500</v>
       </c>
       <c r="I9" s="3">
-        <v>151500</v>
+        <v>1079700</v>
       </c>
       <c r="J9" s="3">
-        <v>167400</v>
+        <v>1117400</v>
       </c>
       <c r="K9" s="3">
         <v>169900</v>
@@ -800,25 +800,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>307000</v>
+        <v>306700</v>
       </c>
       <c r="E10" s="3">
-        <v>207700</v>
+        <v>265100</v>
       </c>
       <c r="F10" s="3">
-        <v>266800</v>
+        <v>266200</v>
       </c>
       <c r="G10" s="3">
-        <v>288100</v>
+        <v>287900</v>
       </c>
       <c r="H10" s="3">
-        <v>71500</v>
+        <v>250200</v>
       </c>
       <c r="I10" s="3">
-        <v>70200</v>
+        <v>228200</v>
       </c>
       <c r="J10" s="3">
-        <v>63900</v>
+        <v>256100</v>
       </c>
       <c r="K10" s="3">
         <v>77400</v>
@@ -934,25 +934,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="3">
-        <v>6300</v>
+        <v>6800</v>
       </c>
       <c r="F14" s="3">
-        <v>33900</v>
+        <v>23600</v>
       </c>
       <c r="G14" s="3">
-        <v>187700</v>
+        <v>112200</v>
       </c>
       <c r="H14" s="3">
-        <v>2600</v>
+        <v>781600</v>
       </c>
       <c r="I14" s="3">
-        <v>-41200</v>
+        <v>145100</v>
       </c>
       <c r="J14" s="3">
-        <v>117000</v>
+        <v>125600</v>
       </c>
       <c r="K14" s="3">
         <v>-500</v>
@@ -976,7 +976,7 @@
         <v>70600</v>
       </c>
       <c r="E15" s="3">
-        <v>49600</v>
+        <v>66500</v>
       </c>
       <c r="F15" s="3">
         <v>75000</v>
@@ -985,13 +985,13 @@
         <v>70100</v>
       </c>
       <c r="H15" s="3">
-        <v>37600</v>
+        <v>99100</v>
       </c>
       <c r="I15" s="3">
-        <v>39500</v>
+        <v>124900</v>
       </c>
       <c r="J15" s="3">
-        <v>45700</v>
+        <v>124000</v>
       </c>
       <c r="K15" s="3">
         <v>49300</v>
@@ -1026,25 +1026,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1236800</v>
+        <v>1209200</v>
       </c>
       <c r="E17" s="3">
-        <v>892800</v>
+        <v>-1221000</v>
       </c>
       <c r="F17" s="3">
-        <v>1186800</v>
+        <v>-1426700</v>
       </c>
       <c r="G17" s="3">
-        <v>1308700</v>
+        <v>1070400</v>
       </c>
       <c r="H17" s="3">
-        <v>229400</v>
+        <v>1192600</v>
       </c>
       <c r="I17" s="3">
-        <v>193400</v>
+        <v>1388400</v>
       </c>
       <c r="J17" s="3">
-        <v>367800</v>
+        <v>1414400</v>
       </c>
       <c r="K17" s="3">
         <v>250100</v>
@@ -1065,25 +1065,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>60700</v>
+        <v>55100</v>
       </c>
       <c r="E18" s="3">
-        <v>29800</v>
+        <v>2395100</v>
       </c>
       <c r="F18" s="3">
-        <v>-1600</v>
+        <v>2565700</v>
       </c>
       <c r="G18" s="3">
-        <v>-130700</v>
+        <v>68600</v>
       </c>
       <c r="H18" s="3">
-        <v>-3300</v>
+        <v>-2000</v>
       </c>
       <c r="I18" s="3">
-        <v>28200</v>
+        <v>-80400</v>
       </c>
       <c r="J18" s="3">
-        <v>-136500</v>
+        <v>-40900</v>
       </c>
       <c r="K18" s="3">
         <v>-2900</v>
@@ -1121,25 +1121,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1200</v>
+        <v>3100</v>
       </c>
       <c r="E20" s="3">
-        <v>22000</v>
+        <v>2325500</v>
       </c>
       <c r="F20" s="3">
-        <v>38700</v>
+        <v>2505200</v>
       </c>
       <c r="G20" s="3">
-        <v>125300</v>
+        <v>-36900</v>
       </c>
       <c r="H20" s="3">
-        <v>2400</v>
+        <v>-185800</v>
       </c>
       <c r="I20" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="J20" s="3">
-        <v>500</v>
+        <v>-15600</v>
       </c>
       <c r="K20" s="3">
         <v>800</v>
@@ -1160,25 +1160,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>145000</v>
+        <v>122600</v>
       </c>
       <c r="E21" s="3">
-        <v>111600</v>
+        <v>136100</v>
       </c>
       <c r="F21" s="3">
-        <v>124300</v>
+        <v>135500</v>
       </c>
       <c r="G21" s="3">
-        <v>85100</v>
+        <v>175600</v>
       </c>
       <c r="H21" s="3">
-        <v>36700</v>
+        <v>283000</v>
       </c>
       <c r="I21" s="3">
-        <v>68900</v>
+        <v>43700</v>
       </c>
       <c r="J21" s="3">
-        <v>-90200</v>
+        <v>98700</v>
       </c>
       <c r="K21" s="3">
         <v>47300</v>
@@ -1211,13 +1211,13 @@
         <v>51300</v>
       </c>
       <c r="H22" s="3">
-        <v>13900</v>
+        <v>151600</v>
       </c>
       <c r="I22" s="3">
-        <v>15100</v>
+        <v>113500</v>
       </c>
       <c r="J22" s="3">
-        <v>16800</v>
+        <v>77700</v>
       </c>
       <c r="K22" s="3">
         <v>17300</v>
@@ -1250,13 +1250,13 @@
         <v>-56600</v>
       </c>
       <c r="H23" s="3">
-        <v>-14700</v>
+        <v>-747800</v>
       </c>
       <c r="I23" s="3">
-        <v>14200</v>
+        <v>-336300</v>
       </c>
       <c r="J23" s="3">
-        <v>-152700</v>
+        <v>-228000</v>
       </c>
       <c r="K23" s="3">
         <v>-19400</v>
@@ -1280,7 +1280,7 @@
         <v>24900</v>
       </c>
       <c r="E24" s="3">
-        <v>7500</v>
+        <v>10800</v>
       </c>
       <c r="F24" s="3">
         <v>11300</v>
@@ -1289,13 +1289,13 @@
         <v>-400</v>
       </c>
       <c r="H24" s="3">
-        <v>-700</v>
+        <v>-50700</v>
       </c>
       <c r="I24" s="3">
-        <v>2900</v>
+        <v>-200</v>
       </c>
       <c r="J24" s="3">
-        <v>-52700</v>
+        <v>-30900</v>
       </c>
       <c r="K24" s="3">
         <v>-3400</v>
@@ -1367,13 +1367,13 @@
         <v>-56300</v>
       </c>
       <c r="H26" s="3">
-        <v>-14000</v>
+        <v>-697100</v>
       </c>
       <c r="I26" s="3">
-        <v>11300</v>
+        <v>-336100</v>
       </c>
       <c r="J26" s="3">
-        <v>-100000</v>
+        <v>-197100</v>
       </c>
       <c r="K26" s="3">
         <v>-16000</v>
@@ -1403,16 +1403,16 @@
         <v>-15800</v>
       </c>
       <c r="G27" s="3">
-        <v>76900</v>
+        <v>76800</v>
       </c>
       <c r="H27" s="3">
-        <v>-3600</v>
+        <v>-723000</v>
       </c>
       <c r="I27" s="3">
-        <v>13600</v>
+        <v>-336900</v>
       </c>
       <c r="J27" s="3">
-        <v>-98200</v>
+        <v>-194700</v>
       </c>
       <c r="K27" s="3">
         <v>-8000</v>
@@ -1471,26 +1471,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1589,25 +1589,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1200</v>
+        <v>-3100</v>
       </c>
       <c r="E32" s="3">
-        <v>-22000</v>
+        <v>-2325500</v>
       </c>
       <c r="F32" s="3">
-        <v>-38700</v>
+        <v>-2505200</v>
       </c>
       <c r="G32" s="3">
-        <v>-125300</v>
+        <v>36900</v>
       </c>
       <c r="H32" s="3">
-        <v>-2400</v>
+        <v>185800</v>
       </c>
       <c r="I32" s="3">
-        <v>-1100</v>
+        <v>-700</v>
       </c>
       <c r="J32" s="3">
-        <v>-500</v>
+        <v>15600</v>
       </c>
       <c r="K32" s="3">
         <v>-800</v>
@@ -1637,16 +1637,16 @@
         <v>-15800</v>
       </c>
       <c r="G33" s="3">
-        <v>76900</v>
+        <v>-56100</v>
       </c>
       <c r="H33" s="3">
-        <v>-3600</v>
+        <v>-697200</v>
       </c>
       <c r="I33" s="3">
-        <v>13600</v>
+        <v>-336800</v>
       </c>
       <c r="J33" s="3">
-        <v>-28200</v>
+        <v>-194700</v>
       </c>
       <c r="K33" s="3">
         <v>-8000</v>
@@ -1715,16 +1715,16 @@
         <v>-15800</v>
       </c>
       <c r="G35" s="3">
-        <v>76900</v>
+        <v>-56100</v>
       </c>
       <c r="H35" s="3">
-        <v>-3600</v>
+        <v>-697200</v>
       </c>
       <c r="I35" s="3">
-        <v>13600</v>
+        <v>-336800</v>
       </c>
       <c r="J35" s="3">
-        <v>-28200</v>
+        <v>-194700</v>
       </c>
       <c r="K35" s="3">
         <v>-8000</v>
@@ -1762,13 +1762,13 @@
         <v>44286</v>
       </c>
       <c r="H38" s="2">
-        <v>43830</v>
+        <v>43921</v>
       </c>
       <c r="I38" s="2">
-        <v>43465</v>
+        <v>43555</v>
       </c>
       <c r="J38" s="2">
-        <v>43100</v>
+        <v>43190</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1835,13 +1835,13 @@
         <v>228000</v>
       </c>
       <c r="H41" s="3">
-        <v>117400</v>
+        <v>196700</v>
       </c>
       <c r="I41" s="3">
-        <v>50800</v>
+        <v>178100</v>
       </c>
       <c r="J41" s="3">
-        <v>13600</v>
+        <v>380200</v>
       </c>
       <c r="K41" s="3">
         <v>26900</v>
@@ -1913,13 +1913,13 @@
         <v>215600</v>
       </c>
       <c r="H43" s="3">
-        <v>56200</v>
+        <v>180700</v>
       </c>
       <c r="I43" s="3">
-        <v>42600</v>
+        <v>216800</v>
       </c>
       <c r="J43" s="3">
-        <v>43400</v>
+        <v>247000</v>
       </c>
       <c r="K43" s="3">
         <v>38600</v>
@@ -1952,13 +1952,13 @@
         <v>92200</v>
       </c>
       <c r="H44" s="3">
-        <v>20100</v>
+        <v>82400</v>
       </c>
       <c r="I44" s="3">
-        <v>20700</v>
+        <v>121300</v>
       </c>
       <c r="J44" s="3">
-        <v>21100</v>
+        <v>129600</v>
       </c>
       <c r="K44" s="3">
         <v>25400</v>
@@ -1978,26 +1978,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>48800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>36100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>30700</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>49900</v>
+        <v>14800</v>
       </c>
       <c r="H45" s="3">
-        <v>2200</v>
+        <v>32400</v>
       </c>
       <c r="I45" s="3">
-        <v>1800</v>
+        <v>17000</v>
       </c>
       <c r="J45" s="3">
-        <v>4500</v>
+        <v>41900</v>
       </c>
       <c r="K45" s="3">
         <v>5400</v>
@@ -2030,13 +2030,13 @@
         <v>585700</v>
       </c>
       <c r="H46" s="3">
-        <v>195900</v>
+        <v>524200</v>
       </c>
       <c r="I46" s="3">
-        <v>115900</v>
+        <v>565500</v>
       </c>
       <c r="J46" s="3">
-        <v>82600</v>
+        <v>834400</v>
       </c>
       <c r="K46" s="3">
         <v>96400</v>
@@ -2069,13 +2069,13 @@
         <v>37500</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>110100</v>
       </c>
       <c r="I47" s="3">
-        <v>27100</v>
+        <v>118200</v>
       </c>
       <c r="J47" s="3">
-        <v>30100</v>
+        <v>131500</v>
       </c>
       <c r="K47" s="3">
         <v>29300</v>
@@ -2108,13 +2108,13 @@
         <v>1251200</v>
       </c>
       <c r="H48" s="3">
-        <v>566400</v>
+        <v>1182700</v>
       </c>
       <c r="I48" s="3">
-        <v>599200</v>
+        <v>1834200</v>
       </c>
       <c r="J48" s="3">
-        <v>673900</v>
+        <v>2068000</v>
       </c>
       <c r="K48" s="3">
         <v>821800</v>
@@ -2135,25 +2135,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>65800</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>83900</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>108800</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>1100</v>
+        <v>19800</v>
       </c>
       <c r="J49" s="3">
-        <v>1100</v>
+        <v>25200</v>
       </c>
       <c r="K49" s="3">
         <v>1100</v>
@@ -2252,25 +2252,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>89700</v>
+        <v>127400</v>
       </c>
       <c r="E52" s="3">
-        <v>79800</v>
+        <v>145600</v>
       </c>
       <c r="F52" s="3">
-        <v>6800</v>
+        <v>90700</v>
       </c>
       <c r="G52" s="3">
-        <v>9000</v>
+        <v>117800</v>
       </c>
       <c r="H52" s="3">
-        <v>2200</v>
+        <v>128300</v>
       </c>
       <c r="I52" s="3">
-        <v>21600</v>
+        <v>77800</v>
       </c>
       <c r="J52" s="3">
-        <v>4400</v>
+        <v>18000</v>
       </c>
       <c r="K52" s="3">
         <v>6600</v>
@@ -2342,13 +2342,13 @@
         <v>1992300</v>
       </c>
       <c r="H54" s="3">
-        <v>764500</v>
+        <v>1945300</v>
       </c>
       <c r="I54" s="3">
-        <v>764900</v>
+        <v>2652600</v>
       </c>
       <c r="J54" s="3">
-        <v>792100</v>
+        <v>3170400</v>
       </c>
       <c r="K54" s="3">
         <v>955200</v>
@@ -2415,13 +2415,13 @@
         <v>69500</v>
       </c>
       <c r="H57" s="3">
-        <v>12900</v>
+        <v>52100</v>
       </c>
       <c r="I57" s="3">
-        <v>13200</v>
+        <v>99600</v>
       </c>
       <c r="J57" s="3">
-        <v>16400</v>
+        <v>101300</v>
       </c>
       <c r="K57" s="3">
         <v>8900</v>
@@ -2442,25 +2442,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13200</v>
+        <v>88500</v>
       </c>
       <c r="E58" s="3">
-        <v>11700</v>
+        <v>87900</v>
       </c>
       <c r="F58" s="3">
-        <v>12800</v>
+        <v>82600</v>
       </c>
       <c r="G58" s="3">
-        <v>16000</v>
+        <v>93900</v>
       </c>
       <c r="H58" s="3">
-        <v>18300</v>
+        <v>127200</v>
       </c>
       <c r="I58" s="3">
-        <v>2100</v>
+        <v>1418600</v>
       </c>
       <c r="J58" s="3">
-        <v>2700</v>
+        <v>1484400</v>
       </c>
       <c r="K58" s="3">
         <v>2100</v>
@@ -2481,25 +2481,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>208700</v>
+        <v>28500</v>
       </c>
       <c r="E59" s="3">
-        <v>184300</v>
+        <v>21000</v>
       </c>
       <c r="F59" s="3">
-        <v>211500</v>
+        <v>28600</v>
       </c>
       <c r="G59" s="3">
-        <v>219600</v>
+        <v>33600</v>
       </c>
       <c r="H59" s="3">
-        <v>19500</v>
+        <v>18400</v>
       </c>
       <c r="I59" s="3">
-        <v>13600</v>
+        <v>15600</v>
       </c>
       <c r="J59" s="3">
-        <v>13300</v>
+        <v>38500</v>
       </c>
       <c r="K59" s="3">
         <v>14600</v>
@@ -2532,13 +2532,13 @@
         <v>305100</v>
       </c>
       <c r="H60" s="3">
-        <v>50800</v>
+        <v>298000</v>
       </c>
       <c r="I60" s="3">
-        <v>28800</v>
+        <v>1668900</v>
       </c>
       <c r="J60" s="3">
-        <v>32400</v>
+        <v>1786600</v>
       </c>
       <c r="K60" s="3">
         <v>25600</v>
@@ -2559,25 +2559,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>534800</v>
+        <v>749800</v>
       </c>
       <c r="E61" s="3">
-        <v>499800</v>
+        <v>665700</v>
       </c>
       <c r="F61" s="3">
-        <v>512900</v>
+        <v>638400</v>
       </c>
       <c r="G61" s="3">
-        <v>527500</v>
+        <v>695200</v>
       </c>
       <c r="H61" s="3">
-        <v>141800</v>
+        <v>740000</v>
       </c>
       <c r="I61" s="3">
-        <v>160200</v>
+        <v>8200</v>
       </c>
       <c r="J61" s="3">
-        <v>202200</v>
+        <v>11100</v>
       </c>
       <c r="K61" s="3">
         <v>230100</v>
@@ -2598,25 +2598,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>269500</v>
+        <v>11700</v>
       </c>
       <c r="E62" s="3">
-        <v>239700</v>
+        <v>5000</v>
       </c>
       <c r="F62" s="3">
-        <v>188200</v>
+        <v>4800</v>
       </c>
       <c r="G62" s="3">
-        <v>261000</v>
+        <v>6700</v>
       </c>
       <c r="H62" s="3">
-        <v>112400</v>
+        <v>290700</v>
       </c>
       <c r="I62" s="3">
-        <v>109100</v>
+        <v>26200</v>
       </c>
       <c r="J62" s="3">
-        <v>108000</v>
+        <v>37000</v>
       </c>
       <c r="K62" s="3">
         <v>226800</v>
@@ -2754,25 +2754,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1113600</v>
+        <v>1114100</v>
       </c>
       <c r="E66" s="3">
-        <v>1024700</v>
+        <v>1025100</v>
       </c>
       <c r="F66" s="3">
-        <v>988500</v>
+        <v>988900</v>
       </c>
       <c r="G66" s="3">
-        <v>1094700</v>
+        <v>1093600</v>
       </c>
       <c r="H66" s="3">
-        <v>307800</v>
+        <v>1369300</v>
       </c>
       <c r="I66" s="3">
-        <v>301400</v>
+        <v>1840200</v>
       </c>
       <c r="J66" s="3">
-        <v>346400</v>
+        <v>1986900</v>
       </c>
       <c r="K66" s="3">
         <v>486800</v>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>149800</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -2978,13 +2978,13 @@
         <v>227000</v>
       </c>
       <c r="H72" s="3">
-        <v>14700</v>
+        <v>139200</v>
       </c>
       <c r="I72" s="3">
-        <v>18300</v>
+        <v>455600</v>
       </c>
       <c r="J72" s="3">
-        <v>4400</v>
+        <v>794200</v>
       </c>
       <c r="K72" s="3">
         <v>32500</v>
@@ -3134,13 +3134,13 @@
         <v>897600</v>
       </c>
       <c r="H76" s="3">
-        <v>456700</v>
+        <v>426500</v>
       </c>
       <c r="I76" s="3">
-        <v>463400</v>
+        <v>805200</v>
       </c>
       <c r="J76" s="3">
-        <v>445700</v>
+        <v>1176200</v>
       </c>
       <c r="K76" s="3">
         <v>468400</v>
@@ -3217,13 +3217,13 @@
         <v>44286</v>
       </c>
       <c r="H80" s="2">
-        <v>43830</v>
+        <v>43921</v>
       </c>
       <c r="I80" s="2">
-        <v>43465</v>
+        <v>43555</v>
       </c>
       <c r="J80" s="2">
-        <v>43100</v>
+        <v>43190</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -3253,16 +3253,16 @@
         <v>-15800</v>
       </c>
       <c r="G81" s="3">
-        <v>76900</v>
+        <v>-56100</v>
       </c>
       <c r="H81" s="3">
-        <v>-3600</v>
+        <v>-697200</v>
       </c>
       <c r="I81" s="3">
-        <v>13600</v>
+        <v>-336800</v>
       </c>
       <c r="J81" s="3">
-        <v>-28200</v>
+        <v>-194700</v>
       </c>
       <c r="K81" s="3">
         <v>-8000</v>
@@ -3300,10 +3300,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>85600</v>
+        <v>64500</v>
       </c>
       <c r="E83" s="3">
-        <v>59800</v>
+        <v>65900</v>
       </c>
       <c r="F83" s="3">
         <v>87200</v>
@@ -3312,13 +3312,13 @@
         <v>90500</v>
       </c>
       <c r="H83" s="3">
-        <v>37600</v>
+        <v>95900</v>
       </c>
       <c r="I83" s="3">
-        <v>39500</v>
+        <v>124900</v>
       </c>
       <c r="J83" s="3">
-        <v>45700</v>
+        <v>124000</v>
       </c>
       <c r="K83" s="3">
         <v>49300</v>
@@ -3537,7 +3537,7 @@
         <v>32000</v>
       </c>
       <c r="E89" s="3">
-        <v>-13300</v>
+        <v>-7700</v>
       </c>
       <c r="F89" s="3">
         <v>123900</v>
@@ -3546,13 +3546,13 @@
         <v>96800</v>
       </c>
       <c r="H89" s="3">
-        <v>27600</v>
+        <v>-108400</v>
       </c>
       <c r="I89" s="3">
-        <v>54400</v>
+        <v>-109400</v>
       </c>
       <c r="J89" s="3">
-        <v>20100</v>
+        <v>-19500</v>
       </c>
       <c r="K89" s="3">
         <v>58500</v>
@@ -3602,13 +3602,13 @@
         <v>-14800</v>
       </c>
       <c r="H91" s="3">
-        <v>-6600</v>
+        <v>-77700</v>
       </c>
       <c r="I91" s="3">
-        <v>-9200</v>
+        <v>-40900</v>
       </c>
       <c r="J91" s="3">
-        <v>-16800</v>
+        <v>-46300</v>
       </c>
       <c r="K91" s="3">
         <v>-39200</v>
@@ -3719,13 +3719,13 @@
         <v>173300</v>
       </c>
       <c r="H94" s="3">
-        <v>48600</v>
+        <v>-76500</v>
       </c>
       <c r="I94" s="3">
-        <v>22800</v>
+        <v>-26100</v>
       </c>
       <c r="J94" s="3">
-        <v>-6600</v>
+        <v>96900</v>
       </c>
       <c r="K94" s="3">
         <v>-9100</v>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3931,13 +3931,13 @@
         <v>-245600</v>
       </c>
       <c r="H100" s="3">
-        <v>-9400</v>
+        <v>202500</v>
       </c>
       <c r="I100" s="3">
-        <v>-43500</v>
+        <v>-63100</v>
       </c>
       <c r="J100" s="3">
-        <v>-27500</v>
+        <v>189000</v>
       </c>
       <c r="K100" s="3">
         <v>-33000</v>
@@ -3970,13 +3970,13 @@
         <v>7500</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>3400</v>
       </c>
       <c r="I101" s="3">
-        <v>200</v>
+        <v>-3500</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
+        <v>17200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
@@ -4000,7 +4000,7 @@
         <v>20000</v>
       </c>
       <c r="E102" s="3">
-        <v>-102300</v>
+        <v>-96800</v>
       </c>
       <c r="F102" s="3">
         <v>34900</v>
@@ -4009,13 +4009,13 @@
         <v>32000</v>
       </c>
       <c r="H102" s="3">
-        <v>66600</v>
+        <v>21100</v>
       </c>
       <c r="I102" s="3">
-        <v>33900</v>
+        <v>-202200</v>
       </c>
       <c r="J102" s="3">
-        <v>-13900</v>
+        <v>283600</v>
       </c>
       <c r="K102" s="3">
         <v>16200</v>

--- a/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>VTOL</t>
   </si>
@@ -656,185 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1264300</v>
+        <v>1415500</v>
       </c>
       <c r="E8" s="3">
-        <v>1173500</v>
+        <v>1297400</v>
       </c>
       <c r="F8" s="3">
+        <v>1198200</v>
+      </c>
+      <c r="G8" s="3">
         <v>1139100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1139000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1190600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1307900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1373400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>247200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>281800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>331200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>299000</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>957600</v>
+        <v>1042100</v>
       </c>
       <c r="E9" s="3">
-        <v>908400</v>
+        <v>990400</v>
       </c>
       <c r="F9" s="3">
+        <v>932600</v>
+      </c>
+      <c r="G9" s="3">
         <v>872900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>851200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>940500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1079700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1117400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>169900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>171500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>204400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186600</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>306700</v>
+        <v>373400</v>
       </c>
       <c r="E10" s="3">
-        <v>265100</v>
+        <v>307000</v>
       </c>
       <c r="F10" s="3">
+        <v>265600</v>
+      </c>
+      <c r="G10" s="3">
         <v>266200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>287900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>250200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>228200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>256100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>77400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>110400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>126800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>112300</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +862,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,87 +943,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1200</v>
+        <v>15900</v>
       </c>
       <c r="E14" s="3">
-        <v>6800</v>
+        <v>16100</v>
       </c>
       <c r="F14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="G14" s="3">
         <v>23600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>112200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>781600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>145100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>125600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>70600</v>
+        <v>53400</v>
       </c>
       <c r="E15" s="3">
-        <v>66500</v>
+        <v>55600</v>
       </c>
       <c r="F15" s="3">
+        <v>56300</v>
+      </c>
+      <c r="G15" s="3">
         <v>75000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>70100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>99100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>47300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>46300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45600</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,86 +1045,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1209200</v>
+        <v>1268600</v>
       </c>
       <c r="E17" s="3">
-        <v>-1221000</v>
+        <v>1226900</v>
       </c>
       <c r="F17" s="3">
-        <v>-1426700</v>
+        <v>1151100</v>
       </c>
       <c r="G17" s="3">
+        <v>1103800</v>
+      </c>
+      <c r="H17" s="3">
         <v>1070400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1192600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1388400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1414400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>250100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>255900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>291000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>252800</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>55100</v>
+        <v>146900</v>
       </c>
       <c r="E18" s="3">
-        <v>2395100</v>
+        <v>70600</v>
       </c>
       <c r="F18" s="3">
-        <v>2565700</v>
+        <v>47700</v>
       </c>
       <c r="G18" s="3">
+        <v>35300</v>
+      </c>
+      <c r="H18" s="3">
         <v>68600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-80400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-40900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46200</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,203 +1147,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3100</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>2325500</v>
+        <v>3700</v>
       </c>
       <c r="F20" s="3">
-        <v>2505200</v>
+        <v>-32100</v>
       </c>
       <c r="G20" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="H20" s="3">
         <v>-36900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-185800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>122600</v>
+        <v>200100</v>
       </c>
       <c r="E21" s="3">
-        <v>136100</v>
+        <v>122500</v>
       </c>
       <c r="F21" s="3">
+        <v>136000</v>
+      </c>
+      <c r="G21" s="3">
         <v>135500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>175600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>283000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>43700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>98700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>84800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>83700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>92800</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E22" s="3">
         <v>41400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>41500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>51300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>151600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>113500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>77700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18100</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E23" s="3">
         <v>18000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-56600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-747800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-336300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-228000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29100</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E24" s="3">
         <v>24900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-50700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-30900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11700</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,87 +1396,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-56300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-697100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-336100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-197100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17400</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>76800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-723000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-336900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-194700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18000</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1492,8 +1552,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,87 +1648,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3100</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-2325500</v>
+        <v>-3700</v>
       </c>
       <c r="F32" s="3">
-        <v>-2505200</v>
+        <v>32100</v>
       </c>
       <c r="G32" s="3">
+        <v>25200</v>
+      </c>
+      <c r="H32" s="3">
         <v>36900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>185800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-56100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-697200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-336800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-194700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18000</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,92 +1774,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-56100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-697200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-336800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-194700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18000</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,47 +1902,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E41" s="3">
         <v>180300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>160000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>263800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>228000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>196700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>178100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>380200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31300</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1894,87 +1983,96 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E43" s="3">
         <v>234600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>215100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>203800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>215600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>180700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>216800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>247000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>38600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>61300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42500</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E44" s="3">
         <v>99900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>81900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>81700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>92200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>82400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>121300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>129600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>28000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>26900</v>
       </c>
       <c r="N44" s="3">
         <v>26900</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1987,150 +2085,162 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>41900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4500</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>619500</v>
+      </c>
+      <c r="E46" s="3">
         <v>563600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>493100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>579900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>585700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>524200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>565500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>834400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>102500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>107800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>105200</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E47" s="3">
         <v>19900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>110100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>118200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>131500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>35000</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1340500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1215700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1156200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1136100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1251200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1182700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1834200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2068000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>821800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2035100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>863100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>803700</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2150,26 +2260,29 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>19800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>400</v>
       </c>
       <c r="N49" s="3">
         <v>400</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>400</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,48 +2361,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>127400</v>
+        <v>117500</v>
       </c>
       <c r="E52" s="3">
+        <v>138100</v>
+      </c>
+      <c r="F52" s="3">
         <v>145600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>90700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>117800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>128300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>77800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14400</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,48 +2445,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2125200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1937300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1812000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1824300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1992300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1945300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2652600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3170400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>955200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1004400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1017200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>958600</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,242 +2526,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E57" s="3">
         <v>87900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>89600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>63500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>99600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13300</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E58" s="3">
         <v>88500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>87900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>93900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1418600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1484400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2800</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E59" s="3">
         <v>28500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14100</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>325900</v>
+      </c>
+      <c r="E60" s="3">
         <v>309800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>285600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>287800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>305100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>298000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1668900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1786600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30100</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>860100</v>
+      </c>
+      <c r="E61" s="3">
         <v>749800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>665700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>638400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>695200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>740000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>230100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>263700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>282100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>279400</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11700</v>
+        <v>8900</v>
       </c>
       <c r="E62" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>290700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>232500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>219100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>213000</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,48 +2901,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1234000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1114100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1025100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>988900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1093600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1369300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1840200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1986900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>486800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>533000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>556500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>522300</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2900,11 +3067,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>149800</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,48 +3129,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>312800</v>
+      </c>
+      <c r="E72" s="3">
         <v>218000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>224700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>211200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>227000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>139200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>455600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>794200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14700</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,48 +3297,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>891700</v>
+      </c>
+      <c r="E76" s="3">
         <v>823700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>787300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>835800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>897600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>426500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>805200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1176200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>468400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>471300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>460700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>436300</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,92 +3381,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-56100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-697200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-336800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-194700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18000</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,47 +3491,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>64500</v>
+        <v>49100</v>
       </c>
       <c r="E83" s="3">
-        <v>65900</v>
+        <v>49600</v>
       </c>
       <c r="F83" s="3">
+        <v>69600</v>
+      </c>
+      <c r="G83" s="3">
         <v>87200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>90500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>95900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>124900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>124000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>49300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>47300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>46300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45600</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,48 +3740,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>177400</v>
+      </c>
+      <c r="E89" s="3">
         <v>32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>123900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>96800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-108400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-109400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>58500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>78300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>64400</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,47 +3803,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-110100</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,48 +3926,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-47300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>173300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-76500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>96900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-93900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43500</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3781,11 +4014,11 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -3793,11 +4026,14 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-5000</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,124 +4154,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E100" s="3">
         <v>22000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-63500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-245600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>202500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-63100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>189000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-33000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-46000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>26100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>13200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-24200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>17200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E102" s="3">
         <v>20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-96800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-202200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>283600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19800</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VTOL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>VTOL</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1490500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1415500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1297400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1198200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1139100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1139000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1190600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1307900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1373400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>247200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>281800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>331200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>299000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1077400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1017200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>966600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>919300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>872900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>851200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>940500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1079700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1117400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>169900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>171500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>204400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>413100</v>
+      </c>
+      <c r="E10" s="3">
         <v>398300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>330800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>278900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>266200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>287900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>250200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>228200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>256100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>110400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>126800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>112300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15900</v>
+        <v>-5400</v>
       </c>
       <c r="E14" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F14" s="3">
         <v>16100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>112200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>781600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>145100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>125600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2500</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E15" s="3">
         <v>53400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>56300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>75000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>70100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>99100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>47300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>46300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1335600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1268600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1226900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1151100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1103800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1070400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1192600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1388400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1414400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>250100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>255900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>291000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>252800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E18" s="3">
         <v>146900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>70600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>68600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-80400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-40900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>-21500</v>
       </c>
       <c r="E20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-25200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-36900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-185800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>200100</v>
+        <v>235300</v>
       </c>
       <c r="E21" s="3">
+        <v>195600</v>
+      </c>
+      <c r="F21" s="3">
         <v>122500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>136000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>135500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>175600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>283000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>98700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>84800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>83700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>92800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E22" s="3">
         <v>37600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>51300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>151600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>113500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18100</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E23" s="3">
         <v>102100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-56600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-747800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-336300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-228000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E24" s="3">
         <v>7200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-50700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-30900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E26" s="3">
         <v>94900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-697100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-336100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-197100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E27" s="3">
         <v>94800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-723000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-336900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-194700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1555,8 +1615,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>21500</v>
       </c>
       <c r="E32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>25200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>36900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>185800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E33" s="3">
         <v>94800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-56100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-697200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-336800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-194700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E35" s="3">
         <v>94800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-56100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-697200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-336800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-194700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>286200</v>
+      </c>
+      <c r="E41" s="3">
         <v>247500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>160000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>263800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>228000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>196700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>178100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>380200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1986,93 +2075,102 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>217100</v>
+      </c>
+      <c r="E43" s="3">
         <v>211600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>234600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>215100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>203800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>215600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>180700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>216800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>247000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E44" s="3">
         <v>114500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>99900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>81900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>81700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>82400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>121300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>129600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>26900</v>
       </c>
       <c r="O44" s="3">
         <v>26900</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2088,167 +2186,179 @@
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>41900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>694300</v>
+      </c>
+      <c r="E46" s="3">
         <v>619500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>563600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>493100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>579900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>585700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>524200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>565500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>834400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>102500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>107800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>105200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E47" s="3">
         <v>22400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>37500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>110100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>118200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>131500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>35000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1394300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1340500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1215700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1156200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1136100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1251200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1182700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1834200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2068000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>821800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2035100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>863100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>803700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2263,26 +2373,29 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>19800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>400</v>
       </c>
       <c r="O49" s="3">
         <v>400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>117500</v>
+        <v>143300</v>
       </c>
       <c r="E52" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F52" s="3">
         <v>138100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>145600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>90700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>117800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>128300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>77800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2311300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2125200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1937300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1812000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1824300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1992300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1945300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2652600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3170400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>955200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1004400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1017200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>958600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E57" s="3">
         <v>83500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>89600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>99600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E58" s="3">
         <v>97000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>88500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>87900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>93900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>127200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1418600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1484400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2800</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E59" s="3">
         <v>31400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E60" s="3">
         <v>325900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>309800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>285600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>287800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>305100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>298000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1668900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1786600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30100</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>808100</v>
+      </c>
+      <c r="E61" s="3">
         <v>860100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>749800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>665700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>638400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>695200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>740000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>230100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>263700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>282100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>279400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8900</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>600</v>
+      </c>
+      <c r="F62" s="3">
         <v>11800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>290700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>226800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>232500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>219100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>213000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1251600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1234000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1114100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1025100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>988900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1093600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1369300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1840200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1986900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>486800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>533000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>556500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>522300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3070,11 +3237,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>149800</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>441700</v>
+      </c>
+      <c r="E72" s="3">
         <v>312800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>218000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>224700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>211200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>227000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>139200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>455600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>794200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>32500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1059700</v>
+      </c>
+      <c r="E76" s="3">
         <v>891700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>823700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>787300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>835800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>897600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>426500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>805200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1176200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>468400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>471300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>460700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>436300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E81" s="3">
         <v>94800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-56100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-697200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-336800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-194700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E83" s="3">
         <v>49100</v>
       </c>
-      <c r="E83" s="3">
-        <v>49600</v>
-      </c>
       <c r="F83" s="3">
+        <v>70600</v>
+      </c>
+      <c r="G83" s="3">
         <v>69600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>87200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>90500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>95900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>124900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>124000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>46300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E89" s="3">
         <v>177400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>123900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>96800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-108400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-109400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>58500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>78300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-255400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-81500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-60100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-110100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-87300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-246000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-47300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>173300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-76500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>96900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-93900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4017,11 +4250,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4029,11 +4262,14 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-5000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E100" s="3">
         <v>141100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>22000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-63500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-245600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>202500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-63100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>189000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-33000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-46000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>26100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-24200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>17200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E102" s="3">
         <v>67600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-96800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-202200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>283600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
